--- a/input/mapping/028. OCB_GOLD_TCKH_V_SLGD_HOP.xlsx
+++ b/input/mapping/028. OCB_GOLD_TCKH_V_SLGD_HOP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/HOP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="346" documentId="13_ncr:1_{82C45277-8561-4971-BEC1-8042A5E437B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53E1044A-1682-481D-8990-0114151764E3}"/>
+  <xr:revisionPtr revIDLastSave="347" documentId="13_ncr:1_{82C45277-8561-4971-BEC1-8042A5E437B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72508BD8-4F96-4AC7-8E48-70C64BD2DCB7}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -711,7 +711,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -806,6 +806,21 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -836,12 +851,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -863,18 +872,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1217,155 +1220,155 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="30" customHeight="1">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="51"/>
-      <c r="O1" s="51"/>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
+      <c r="Q1" s="56"/>
     </row>
     <row r="2" spans="1:17" ht="21.95" customHeight="1">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
       <c r="F2" s="4"/>
-      <c r="G2" s="42" t="s">
+      <c r="G2" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="44"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="49"/>
       <c r="K2" s="4"/>
-      <c r="L2" s="57" t="s">
+      <c r="L2" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="M2" s="58"/>
-      <c r="N2" s="58"/>
-      <c r="O2" s="58"/>
-      <c r="P2" s="58"/>
-      <c r="Q2" s="58"/>
+      <c r="M2" s="61"/>
+      <c r="N2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
     </row>
     <row r="3" spans="1:17" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
       <c r="F3" s="4"/>
-      <c r="G3" s="45" t="s">
+      <c r="G3" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="46"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="47"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="52"/>
       <c r="K3" s="4"/>
-      <c r="L3" s="55" t="s">
+      <c r="L3" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="56"/>
-      <c r="N3" s="56"/>
-      <c r="O3" s="56"/>
-      <c r="P3" s="56"/>
-      <c r="Q3" s="56"/>
+      <c r="M3" s="59"/>
+      <c r="N3" s="59"/>
+      <c r="O3" s="59"/>
+      <c r="P3" s="59"/>
+      <c r="Q3" s="59"/>
     </row>
     <row r="4" spans="1:17" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="48"/>
-      <c r="B4" s="49"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
+      <c r="A4" s="53"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
       <c r="F4" s="4"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="50"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="55"/>
       <c r="K4" s="4"/>
-      <c r="L4" s="55"/>
-      <c r="M4" s="56"/>
-      <c r="N4" s="56"/>
-      <c r="O4" s="56"/>
-      <c r="P4" s="56"/>
-      <c r="Q4" s="56"/>
+      <c r="L4" s="58"/>
+      <c r="M4" s="59"/>
+      <c r="N4" s="59"/>
+      <c r="O4" s="59"/>
+      <c r="P4" s="59"/>
+      <c r="Q4" s="59"/>
     </row>
     <row r="5" spans="1:17" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="48"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
+      <c r="A5" s="53"/>
+      <c r="B5" s="54"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
       <c r="F5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="48"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="50"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="55"/>
       <c r="K5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L5" s="55"/>
-      <c r="M5" s="56"/>
-      <c r="N5" s="56"/>
-      <c r="O5" s="56"/>
-      <c r="P5" s="56"/>
-      <c r="Q5" s="56"/>
+      <c r="L5" s="58"/>
+      <c r="M5" s="59"/>
+      <c r="N5" s="59"/>
+      <c r="O5" s="59"/>
+      <c r="P5" s="59"/>
+      <c r="Q5" s="59"/>
     </row>
     <row r="6" spans="1:17" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="48"/>
-      <c r="B6" s="49"/>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
+      <c r="A6" s="53"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
       <c r="F6" s="4"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="50"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="55"/>
       <c r="K6" s="4"/>
-      <c r="L6" s="55"/>
-      <c r="M6" s="56"/>
-      <c r="N6" s="56"/>
-      <c r="O6" s="56"/>
-      <c r="P6" s="56"/>
-      <c r="Q6" s="56"/>
+      <c r="L6" s="58"/>
+      <c r="M6" s="59"/>
+      <c r="N6" s="59"/>
+      <c r="O6" s="59"/>
+      <c r="P6" s="59"/>
+      <c r="Q6" s="59"/>
     </row>
     <row r="7" spans="1:17" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="48"/>
-      <c r="B7" s="49"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
+      <c r="A7" s="53"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
       <c r="F7" s="4"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49"/>
-      <c r="J7" s="50"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="55"/>
       <c r="K7" s="4"/>
-      <c r="L7" s="55"/>
-      <c r="M7" s="56"/>
-      <c r="N7" s="56"/>
-      <c r="O7" s="56"/>
-      <c r="P7" s="56"/>
-      <c r="Q7" s="56"/>
+      <c r="L7" s="58"/>
+      <c r="M7" s="59"/>
+      <c r="N7" s="59"/>
+      <c r="O7" s="59"/>
+      <c r="P7" s="59"/>
+      <c r="Q7" s="59"/>
     </row>
     <row r="8" spans="1:17" ht="18" customHeight="1"/>
     <row r="9" spans="1:17" ht="18" customHeight="1">
@@ -1474,86 +1477,74 @@
       <c r="J27" s="2"/>
     </row>
     <row r="28" spans="2:10" ht="20.100000000000001" customHeight="1">
-      <c r="B28" s="54"/>
-      <c r="C28" s="54"/>
-      <c r="D28" s="54"/>
-      <c r="E28" s="54"/>
-      <c r="F28" s="54"/>
-      <c r="G28" s="54"/>
-      <c r="H28" s="54"/>
-      <c r="I28" s="54"/>
-      <c r="J28" s="54"/>
+      <c r="B28" s="57"/>
+      <c r="C28" s="57"/>
+      <c r="D28" s="57"/>
+      <c r="E28" s="57"/>
+      <c r="F28" s="57"/>
+      <c r="G28" s="57"/>
+      <c r="H28" s="57"/>
+      <c r="I28" s="57"/>
+      <c r="J28" s="57"/>
     </row>
     <row r="29" spans="2:10" ht="27.95" customHeight="1">
-      <c r="B29" s="53"/>
-      <c r="C29" s="53"/>
-      <c r="D29" s="53"/>
-      <c r="E29" s="52"/>
-      <c r="F29" s="52"/>
-      <c r="G29" s="61"/>
-      <c r="H29" s="61"/>
-      <c r="I29" s="61"/>
-      <c r="J29" s="61"/>
+      <c r="B29" s="44"/>
+      <c r="C29" s="44"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="46"/>
+      <c r="F29" s="46"/>
+      <c r="G29" s="45"/>
+      <c r="H29" s="45"/>
+      <c r="I29" s="45"/>
+      <c r="J29" s="45"/>
     </row>
     <row r="30" spans="2:10" ht="27.95" customHeight="1">
-      <c r="B30" s="53"/>
-      <c r="C30" s="53"/>
-      <c r="D30" s="53"/>
-      <c r="E30" s="52"/>
-      <c r="F30" s="52"/>
-      <c r="G30" s="61"/>
-      <c r="H30" s="61"/>
-      <c r="I30" s="61"/>
-      <c r="J30" s="61"/>
+      <c r="B30" s="44"/>
+      <c r="C30" s="44"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="46"/>
+      <c r="F30" s="46"/>
+      <c r="G30" s="45"/>
+      <c r="H30" s="45"/>
+      <c r="I30" s="45"/>
+      <c r="J30" s="45"/>
     </row>
     <row r="31" spans="2:10" ht="27.95" customHeight="1">
-      <c r="B31" s="53"/>
-      <c r="C31" s="53"/>
-      <c r="D31" s="53"/>
-      <c r="E31" s="52"/>
-      <c r="F31" s="52"/>
-      <c r="G31" s="61"/>
-      <c r="H31" s="61"/>
-      <c r="I31" s="61"/>
-      <c r="J31" s="61"/>
+      <c r="B31" s="44"/>
+      <c r="C31" s="44"/>
+      <c r="D31" s="44"/>
+      <c r="E31" s="46"/>
+      <c r="F31" s="46"/>
+      <c r="G31" s="45"/>
+      <c r="H31" s="45"/>
+      <c r="I31" s="45"/>
+      <c r="J31" s="45"/>
     </row>
     <row r="32" spans="2:10" ht="27.95" customHeight="1">
-      <c r="B32" s="53"/>
-      <c r="C32" s="53"/>
-      <c r="D32" s="53"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="52"/>
-      <c r="G32" s="61"/>
-      <c r="H32" s="61"/>
-      <c r="I32" s="61"/>
-      <c r="J32" s="61"/>
+      <c r="B32" s="44"/>
+      <c r="C32" s="44"/>
+      <c r="D32" s="44"/>
+      <c r="E32" s="46"/>
+      <c r="F32" s="46"/>
+      <c r="G32" s="45"/>
+      <c r="H32" s="45"/>
+      <c r="I32" s="45"/>
+      <c r="J32" s="45"/>
     </row>
     <row r="33" spans="2:10" ht="27.95" customHeight="1">
-      <c r="B33" s="53"/>
-      <c r="C33" s="53"/>
-      <c r="D33" s="53"/>
-      <c r="E33" s="52"/>
-      <c r="F33" s="52"/>
-      <c r="G33" s="61"/>
-      <c r="H33" s="61"/>
-      <c r="I33" s="61"/>
-      <c r="J33" s="61"/>
+      <c r="B33" s="44"/>
+      <c r="C33" s="44"/>
+      <c r="D33" s="44"/>
+      <c r="E33" s="46"/>
+      <c r="F33" s="46"/>
+      <c r="G33" s="45"/>
+      <c r="H33" s="45"/>
+      <c r="I33" s="45"/>
+      <c r="J33" s="45"/>
     </row>
     <row r="34" spans="2:10" ht="18" customHeight="1"/>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="G29:J29"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="G32:J32"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:J30"/>
-    <mergeCell ref="G33:J33"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="G31:J31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B31:D31"/>
     <mergeCell ref="G2:J2"/>
     <mergeCell ref="G3:J7"/>
     <mergeCell ref="A1:Q1"/>
@@ -1567,6 +1558,18 @@
     <mergeCell ref="L2:Q2"/>
     <mergeCell ref="A3:E7"/>
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="G29:J29"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="G32:J32"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:J30"/>
+    <mergeCell ref="G33:J33"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="G31:J31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B31:D31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1608,14 +1611,14 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" ht="396.75">
       <c r="A3" t="s">
         <v>24</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="64" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1637,13 +1640,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="7" customFormat="1" ht="15" customHeight="1">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
       <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" s="7" customFormat="1">
@@ -1707,14 +1710,14 @@
       <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6" s="10" customFormat="1" ht="14.45" customHeight="1">
-      <c r="A6" s="63" t="s">
+      <c r="A6" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="63"/>
-      <c r="C6" s="63"/>
-      <c r="D6" s="63"/>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
+      <c r="B6" s="43"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
     </row>
     <row r="7" spans="1:6" s="11" customFormat="1">
       <c r="A7" s="12" t="s">
@@ -1861,12 +1864,13 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2042,17 +2046,16 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97C9CD0F-F06A-4CB4-AECA-A7F437F3D1E1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05B676A7-3FE0-4AFA-BF95-5F9A645EA2A6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2060,5 +2063,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05B676A7-3FE0-4AFA-BF95-5F9A645EA2A6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97C9CD0F-F06A-4CB4-AECA-A7F437F3D1E1}"/>
 </file>